--- a/grupos/5AEV - Estadisticos 20211.xlsx
+++ b/grupos/5AEV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="114">
   <si>
     <t>Materia</t>
   </si>
@@ -158,21 +158,21 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Bautista Sarao Eutiquio</t>
+  </si>
+  <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Bautista Sarao Eutiquio</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -191,166 +191,166 @@
     <t>CABRERA</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>NUÑEZ</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
     <t>CHAVEZ</t>
   </si>
   <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
+    <t>NOGALES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>KARLA IRAN</t>
+  </si>
+  <si>
+    <t>CARLOS ADRIAN</t>
+  </si>
+  <si>
+    <t>GERARDO RAUL</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
+  </si>
+  <si>
+    <t>MARTI NEFTALI</t>
+  </si>
+  <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>ESPINOSA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>NUÑEZ</t>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>MEDRANO</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>DE LOS SANTOS</t>
   </si>
   <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
     <t>GALVEZ</t>
   </si>
   <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VILLAR</t>
   </si>
   <si>
     <t>PACHECO</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>NOGALES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>KARLA IRAN</t>
-  </si>
-  <si>
-    <t>CARLOS ADRIAN</t>
+    <t>LOZANO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
   </si>
   <si>
     <t>EUSEBIO</t>
   </si>
   <si>
+    <t>ALMA LIZETH</t>
+  </si>
+  <si>
     <t>LUIS ARIEL</t>
   </si>
   <si>
-    <t>GERARDO RAUL</t>
+    <t>YASIEL</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
   </si>
   <si>
     <t>MARTIN</t>
   </si>
   <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>VICTOR SAUL</t>
   </si>
   <si>
     <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSUE YAMIN</t>
-  </si>
-  <si>
-    <t>MARTI NEFTALI</t>
-  </si>
-  <si>
-    <t>AGUSTIN</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>MEDRANO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>VILLAR</t>
-  </si>
-  <si>
-    <t>LOZANO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>ALMA LIZETH</t>
-  </si>
-  <si>
-    <t>YASIEL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>VICTOR SAUL</t>
   </si>
   <si>
     <t>JOSE DANIEL</t>
@@ -885,7 +885,7 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -897,7 +897,7 @@
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -927,7 +927,7 @@
         <v>-1</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -971,7 +971,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -995,7 +995,7 @@
         <v>-1</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1003,7 +1003,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C6">
         <v>6</v>
@@ -1021,13 +1021,13 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1039,7 +1039,7 @@
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1066,10 +1066,10 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1081,10 +1081,10 @@
         <v>8</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1113,10 +1113,10 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1128,10 +1128,10 @@
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1155,10 +1155,10 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1170,10 +1170,10 @@
         <v>10</v>
       </c>
       <c r="AB7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1181,7 +1181,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1202,10 +1202,10 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1217,10 +1217,10 @@
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1244,10 +1244,10 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1259,10 +1259,10 @@
         <v>10</v>
       </c>
       <c r="AB8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC8">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1270,7 +1270,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>-1</v>
@@ -1285,13 +1285,13 @@
         <v>-1</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1306,7 +1306,7 @@
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1333,7 +1333,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>-1</v>
@@ -1348,10 +1348,10 @@
         <v>-1</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1380,10 +1380,10 @@
         <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1395,10 +1395,10 @@
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1422,7 +1422,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1466,13 +1466,13 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1484,10 +1484,10 @@
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1511,7 +1511,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1529,7 +1529,7 @@
         <v>9</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1537,7 +1537,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1558,10 +1558,10 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1573,10 +1573,10 @@
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1600,7 +1600,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>6</v>
@@ -1615,10 +1615,10 @@
         <v>6</v>
       </c>
       <c r="AB12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1647,10 +1647,10 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1662,10 +1662,10 @@
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1692,7 +1692,7 @@
         <v>9</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>10</v>
@@ -1704,10 +1704,10 @@
         <v>9</v>
       </c>
       <c r="AB13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1739,7 +1739,7 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1751,10 +1751,10 @@
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1781,7 +1781,7 @@
         <v>7</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1793,10 +1793,10 @@
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1822,13 +1822,13 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1840,7 +1840,7 @@
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1882,10 +1882,10 @@
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1914,10 +1914,10 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1929,10 +1929,10 @@
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1974,7 +1974,7 @@
         <v>9</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2003,10 +2003,10 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2018,10 +2018,10 @@
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2045,7 +2045,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2060,10 +2060,10 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2086,10 +2086,10 @@
         <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2149,10 +2149,10 @@
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2160,7 +2160,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>8</v>
@@ -2181,10 +2181,10 @@
         <v>9</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2196,7 +2196,7 @@
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2223,10 +2223,10 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2238,7 +2238,7 @@
         <v>6</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>9</v>
@@ -2270,10 +2270,10 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2285,10 +2285,10 @@
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2312,10 +2312,10 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2327,10 +2327,10 @@
         <v>6</v>
       </c>
       <c r="AB20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2374,7 +2374,7 @@
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2416,7 +2416,7 @@
         <v>10</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>8</v>
@@ -2463,7 +2463,7 @@
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2505,7 +2505,7 @@
         <v>-1</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC22">
         <v>10</v>
@@ -2537,10 +2537,10 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -2552,10 +2552,10 @@
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2579,7 +2579,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2597,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2605,10 +2605,10 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>-1</v>
@@ -2620,16 +2620,16 @@
         <v>-1</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2641,7 +2641,7 @@
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2668,10 +2668,10 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>-1</v>
@@ -2683,10 +2683,10 @@
         <v>-1</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2697,7 +2697,7 @@
         <v>-1</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>-1</v>
@@ -2712,13 +2712,13 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -2730,7 +2730,7 @@
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2760,7 +2760,7 @@
         <v>-1</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y25">
         <v>-1</v>
@@ -2772,10 +2772,10 @@
         <v>-1</v>
       </c>
       <c r="AB25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2819,7 +2819,7 @@
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2861,7 +2861,7 @@
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -2952,7 +2952,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>46</v>
@@ -2961,97 +2961,97 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>50</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
       </c>
       <c r="C4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>69.56999999999999</v>
+        <v>77.27</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>30.43</v>
+        <v>22.73</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>6.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6">
         <v>23</v>
@@ -3069,7 +3069,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -3080,66 +3080,66 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
       </c>
       <c r="C7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>18</v>
       </c>
       <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>81.81999999999999</v>
+      </c>
+      <c r="G7">
+        <v>18.18</v>
+      </c>
+      <c r="H7">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>78.26000000000001</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>8.4</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>21.74</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>50</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>19</v>
       </c>
       <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>82.61</v>
+      </c>
+      <c r="G8">
+        <v>17.39</v>
+      </c>
+      <c r="H8">
+        <v>7.8</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="F8">
-        <v>86.36</v>
-      </c>
-      <c r="G8">
+      <c r="J8">
         <v>0</v>
-      </c>
-      <c r="H8">
-        <v>8.4</v>
-      </c>
-      <c r="I8">
-        <v>3</v>
-      </c>
-      <c r="J8">
-        <v>13.64</v>
       </c>
     </row>
   </sheetData>
@@ -3149,7 +3149,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3184,16 +3184,16 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3204,10 +3204,10 @@
         <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3224,10 +3224,10 @@
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -3244,16 +3244,16 @@
         <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3264,53 +3264,53 @@
         <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920045</v>
+        <v>19330051920055</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920045</v>
+        <v>19330051920058</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>47</v>
@@ -3318,19 +3318,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920049</v>
+        <v>19330051920050</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>46</v>
@@ -3338,16 +3338,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920055</v>
+        <v>19330051920050</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -3358,156 +3358,156 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920055</v>
+        <v>19330051920050</v>
       </c>
       <c r="B11" t="s">
         <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920056</v>
+        <v>19330051920050</v>
       </c>
       <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
         <v>60</v>
       </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920058</v>
+        <v>19330051920067</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920058</v>
+        <v>19330051920067</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920050</v>
+        <v>19330051920067</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920050</v>
+        <v>19330051920067</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>19330051920050</v>
+        <v>18330051920078</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>19330051920050</v>
+        <v>18330051920078</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -3518,119 +3518,119 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920050</v>
+        <v>18330051920078</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920050</v>
+        <v>19330051920418</v>
       </c>
       <c r="B20" t="s">
         <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>19330051920050</v>
+        <v>19330051920418</v>
       </c>
       <c r="B21" t="s">
         <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>19330051920067</v>
+        <v>19330051920418</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920067</v>
+        <v>19330051920076</v>
       </c>
       <c r="B23" t="s">
         <v>63</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920067</v>
+        <v>19330051920076</v>
       </c>
       <c r="B24" t="s">
         <v>63</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
         <v>48</v>
@@ -3638,402 +3638,42 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920067</v>
+        <v>19330051920076</v>
       </c>
       <c r="B25" t="s">
         <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920067</v>
+        <v>19330051920081</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
         <v>72</v>
       </c>
       <c r="D26" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>19330051920067</v>
-      </c>
-      <c r="B27" t="s">
-        <v>63</v>
-      </c>
-      <c r="C27" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" t="s">
-        <v>86</v>
-      </c>
-      <c r="E27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>19330051920068</v>
-      </c>
-      <c r="B28" t="s">
-        <v>63</v>
-      </c>
-      <c r="C28" t="s">
-        <v>73</v>
-      </c>
-      <c r="D28" t="s">
-        <v>87</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>18330051920078</v>
-      </c>
-      <c r="B29" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" t="s">
-        <v>74</v>
-      </c>
-      <c r="D29" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>18330051920078</v>
-      </c>
-      <c r="B30" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D30" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>18330051920078</v>
-      </c>
-      <c r="B31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>19330051920418</v>
-      </c>
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" t="s">
-        <v>75</v>
-      </c>
-      <c r="D32" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>19330051920418</v>
-      </c>
-      <c r="B33" t="s">
-        <v>65</v>
-      </c>
-      <c r="C33" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E33" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>19330051920418</v>
-      </c>
-      <c r="B34" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" t="s">
-        <v>89</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>19330051920418</v>
-      </c>
-      <c r="B35" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" t="s">
-        <v>75</v>
-      </c>
-      <c r="D35" t="s">
-        <v>89</v>
-      </c>
-      <c r="E35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>19330051920418</v>
-      </c>
-      <c r="B36" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" t="s">
-        <v>75</v>
-      </c>
-      <c r="D36" t="s">
-        <v>89</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920418</v>
-      </c>
-      <c r="B37" t="s">
-        <v>65</v>
-      </c>
-      <c r="C37" t="s">
-        <v>75</v>
-      </c>
-      <c r="D37" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>19330051920418</v>
-      </c>
-      <c r="B38" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38" t="s">
-        <v>75</v>
-      </c>
-      <c r="D38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E38" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>19330051920076</v>
-      </c>
-      <c r="B39" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" t="s">
-        <v>76</v>
-      </c>
-      <c r="D39" t="s">
-        <v>90</v>
-      </c>
-      <c r="E39" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>19330051920076</v>
-      </c>
-      <c r="B40" t="s">
-        <v>66</v>
-      </c>
-      <c r="C40" t="s">
-        <v>76</v>
-      </c>
-      <c r="D40" t="s">
-        <v>90</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>19330051920076</v>
-      </c>
-      <c r="B41" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" t="s">
-        <v>90</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>19330051920076</v>
-      </c>
-      <c r="B42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" t="s">
-        <v>76</v>
-      </c>
-      <c r="D42" t="s">
-        <v>90</v>
-      </c>
-      <c r="E42" t="s">
-        <v>9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>19330051920076</v>
-      </c>
-      <c r="B43" t="s">
-        <v>66</v>
-      </c>
-      <c r="C43" t="s">
-        <v>76</v>
-      </c>
-      <c r="D43" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920081</v>
-      </c>
-      <c r="B44" t="s">
-        <v>67</v>
-      </c>
-      <c r="C44" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" t="s">
-        <v>91</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -4072,81 +3712,81 @@
         <v>19330051920050</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920418</v>
+        <v>19330051920067</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920067</v>
+        <v>18330051920009</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920076</v>
+        <v>18330051920078</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>18330051920009</v>
+        <v>19330051920418</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -4154,16 +3794,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>18330051920078</v>
+        <v>19330051920076</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -4177,10 +3817,10 @@
         <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -4188,132 +3828,132 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920045</v>
+        <v>19330051920055</v>
       </c>
       <c r="B9" t="s">
         <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920055</v>
+        <v>19330051920058</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920058</v>
+        <v>19330051920081</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920049</v>
+        <v>19330051920045</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920056</v>
+        <v>19330051920046</v>
       </c>
       <c r="B13" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920068</v>
+        <v>19330051920049</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920081</v>
+        <v>19330051920053</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920046</v>
+        <v>19330051920057</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>106</v>
@@ -4324,13 +3964,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920053</v>
+        <v>19330051920056</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
         <v>107</v>
@@ -4341,13 +3981,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920057</v>
+        <v>18330051920022</v>
       </c>
       <c r="B18" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D18" t="s">
         <v>108</v>
@@ -4358,16 +3998,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>18330051920022</v>
+        <v>19330051920059</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4375,16 +4015,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920059</v>
+        <v>19330051920064</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4392,13 +4032,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920064</v>
+        <v>19330051920068</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
         <v>110</v>
@@ -4412,10 +4052,10 @@
         <v>19330051920069</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D22" t="s">
         <v>111</v>
@@ -4429,10 +4069,10 @@
         <v>19330051920074</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
         <v>112</v>
@@ -4446,10 +4086,10 @@
         <v>19330051920075</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
         <v>113</v>
@@ -4465,7 +4105,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4497,39 +4137,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920042</v>
+        <v>19330051920045</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>46</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920042</v>
+        <v>19330051920045</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4538,27 +4178,27 @@
         <v>45</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920055</v>
+        <v>19330051920081</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
         <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -4566,62 +4206,62 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920055</v>
+        <v>19330051920081</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
         <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920056</v>
+        <v>19330051920046</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920056</v>
+        <v>19330051920055</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4630,44 +4270,44 @@
         <v>45</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920081</v>
+        <v>19330051920056</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920081</v>
+        <v>18330051920022</v>
       </c>
       <c r="B9" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4681,16 +4321,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920046</v>
+        <v>19330051920074</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4699,98 +4339,6 @@
         <v>45</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920049</v>
-      </c>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>18330051920022</v>
-      </c>
-      <c r="B12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920068</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920074</v>
-      </c>
-      <c r="B14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20211.xlsx
+++ b/grupos/5AEV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="114">
   <si>
     <t>Materia</t>
   </si>
@@ -164,15 +164,15 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Bautista Sarao Eutiquio</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -188,178 +188,178 @@
     <t>ARIZMENDI</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>NUÑEZ</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>NOGALES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>KARLA IRAN</t>
+  </si>
+  <si>
+    <t>ALEXIS ARMANDO</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>JOSUE YAMIN</t>
+  </si>
+  <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>MEDRANO</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>SAN JUAN</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>NUÑEZ</t>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
   </si>
   <si>
     <t>VALIENTE</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VILLAR</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>LOZANO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
   </si>
   <si>
     <t>CANSECO</t>
   </si>
   <si>
-    <t>NOGALES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>KARLA IRAN</t>
-  </si>
-  <si>
     <t>CARLOS ADRIAN</t>
   </si>
   <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>ALMA LIZETH</t>
+  </si>
+  <si>
+    <t>LUIS ARIEL</t>
+  </si>
+  <si>
+    <t>YASIEL</t>
+  </si>
+  <si>
     <t>GERARDO RAUL</t>
   </si>
   <si>
-    <t>ALEXIS ARMANDO</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>ALEXIS YAIR</t>
-  </si>
-  <si>
-    <t>JOSUE YAMIN</t>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
+    <t>VICTOR SAUL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
   </si>
   <si>
     <t>MARTI NEFTALI</t>
-  </si>
-  <si>
-    <t>AGUSTIN</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>MEDRANO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>VILLAR</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>LOZANO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ALMA LIZETH</t>
-  </si>
-  <si>
-    <t>LUIS ARIEL</t>
-  </si>
-  <si>
-    <t>YASIEL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>VICTOR SAUL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
   </si>
 </sst>
 </file>
@@ -870,7 +870,7 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -891,7 +891,7 @@
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -933,7 +933,7 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <v>10</v>
@@ -950,25 +950,25 @@
         <v>14</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H5">
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>8</v>
@@ -986,13 +986,13 @@
         <v>-1</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>7</v>
@@ -1030,13 +1030,13 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>5</v>
@@ -1072,13 +1072,13 @@
         <v>5</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>6</v>
@@ -1119,13 +1119,13 @@
         <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>10</v>
@@ -1208,13 +1208,13 @@
         <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>10</v>
@@ -1253,10 +1253,10 @@
         <v>10</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -1279,7 +1279,7 @@
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F9">
         <v>-1</v>
@@ -1300,7 +1300,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1342,7 +1342,7 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>-1</v>
@@ -1386,13 +1386,13 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>10</v>
@@ -1428,13 +1428,13 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z10">
         <v>8</v>
       </c>
       <c r="AA10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB10">
         <v>10</v>
@@ -1457,7 +1457,7 @@
         <v>9</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F11">
         <v>8</v>
@@ -1475,13 +1475,13 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>9</v>
@@ -1520,10 +1520,10 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB11">
         <v>9</v>
@@ -1564,13 +1564,13 @@
         <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>8</v>
@@ -1606,13 +1606,13 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z12">
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>8</v>
@@ -1653,13 +1653,13 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>10</v>
@@ -1698,10 +1698,10 @@
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -1742,13 +1742,13 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>10</v>
@@ -1784,13 +1784,13 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -1831,10 +1831,10 @@
         <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1873,7 +1873,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <v>5</v>
@@ -1920,13 +1920,13 @@
         <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>8</v>
@@ -1965,7 +1965,7 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA16">
         <v>10</v>
@@ -2009,13 +2009,13 @@
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>10</v>
@@ -2054,7 +2054,7 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>10</v>
@@ -2080,7 +2080,7 @@
         <v>-1</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F18">
         <v>6</v>
@@ -2101,7 +2101,7 @@
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2143,7 +2143,7 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA18">
         <v>6</v>
@@ -2187,13 +2187,13 @@
         <v>6</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>10</v>
@@ -2229,10 +2229,10 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>6</v>
@@ -2276,13 +2276,13 @@
         <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>10</v>
@@ -2321,10 +2321,10 @@
         <v>8</v>
       </c>
       <c r="Z20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>10</v>
@@ -2365,13 +2365,13 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>10</v>
@@ -2413,7 +2413,7 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2436,10 +2436,10 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G22">
         <v>7</v>
@@ -2457,7 +2457,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2499,10 +2499,10 @@
         <v>7</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB22">
         <v>6</v>
@@ -2543,13 +2543,13 @@
         <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>10</v>
@@ -2588,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA23">
         <v>10</v>
@@ -2611,13 +2611,13 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -2632,13 +2632,13 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>5</v>
@@ -2674,13 +2674,13 @@
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB24">
         <v>5</v>
@@ -2724,7 +2724,7 @@
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2810,10 +2810,10 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2852,7 +2852,7 @@
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <v>5</v>
@@ -2929,25 +2929,25 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>34.78</v>
+        <v>30.43</v>
       </c>
       <c r="G2">
-        <v>34.78</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>30.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3016,103 +3016,103 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>18</v>
       </c>
       <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>81.81999999999999</v>
+      </c>
+      <c r="G5">
+        <v>18.18</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>78.26000000000001</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I5">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>21.74</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6">
         <v>23</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>82.61</v>
+      </c>
+      <c r="G6">
+        <v>17.39</v>
+      </c>
+      <c r="H6">
+        <v>7.8</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>78.26000000000001</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>8.4</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>21.74</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>81.81999999999999</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="G7">
-        <v>18.18</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>50</v>
@@ -3121,25 +3121,25 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>82.61</v>
+        <v>91.3</v>
       </c>
       <c r="G8">
-        <v>17.39</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3149,7 +3149,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3184,10 +3184,10 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -3198,481 +3198,241 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>19330051920042</v>
+        <v>19330051920058</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>18330051920009</v>
+        <v>19330051920050</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>18330051920009</v>
+        <v>19330051920050</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>18330051920009</v>
+        <v>19330051920050</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920055</v>
+        <v>19330051920067</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>19330051920058</v>
+        <v>19330051920067</v>
       </c>
       <c r="B8" t="s">
         <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>19330051920050</v>
+        <v>19330051920067</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>19330051920050</v>
+        <v>18330051920078</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>19330051920050</v>
+        <v>19330051920076</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>19330051920050</v>
+        <v>19330051920076</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>19330051920067</v>
+        <v>19330051920076</v>
       </c>
       <c r="B13" t="s">
         <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920067</v>
+        <v>19330051920081</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920067</v>
-      </c>
-      <c r="B15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920067</v>
-      </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>18330051920078</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>18330051920078</v>
-      </c>
-      <c r="B18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>18330051920078</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" t="s">
-        <v>69</v>
-      </c>
-      <c r="D19" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>19330051920418</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>80</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>19330051920418</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>19330051920418</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>19330051920076</v>
-      </c>
-      <c r="B23" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>19330051920076</v>
-      </c>
-      <c r="B24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>19330051920076</v>
-      </c>
-      <c r="B25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>19330051920081</v>
-      </c>
-      <c r="B26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3712,16 +3472,16 @@
         <v>19330051920050</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3729,30 +3489,30 @@
         <v>19330051920067</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>18330051920009</v>
+        <v>19330051920076</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -3760,132 +3520,132 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>18330051920078</v>
+        <v>19330051920042</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920418</v>
+        <v>19330051920058</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920076</v>
+        <v>18330051920078</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920042</v>
+        <v>19330051920081</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920055</v>
+        <v>18330051920009</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920058</v>
+        <v>19330051920045</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920081</v>
+        <v>19330051920046</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920045</v>
+        <v>19330051920049</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
         <v>102</v>
@@ -3896,13 +3656,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920046</v>
+        <v>19330051920053</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
         <v>103</v>
@@ -3913,13 +3673,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920049</v>
+        <v>19330051920055</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
         <v>104</v>
@@ -3930,13 +3690,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920053</v>
+        <v>19330051920057</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
         <v>105</v>
@@ -3947,13 +3707,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920057</v>
+        <v>19330051920056</v>
       </c>
       <c r="B16" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" t="s">
         <v>86</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>106</v>
@@ -3964,13 +3724,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920056</v>
+        <v>18330051920022</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
         <v>107</v>
@@ -3981,16 +3741,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>18330051920022</v>
+        <v>19330051920059</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3998,16 +3758,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920059</v>
+        <v>19330051920064</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4015,13 +3775,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920064</v>
+        <v>19330051920068</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
         <v>109</v>
@@ -4032,13 +3792,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920068</v>
+        <v>19330051920069</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
         <v>110</v>
@@ -4049,13 +3809,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920069</v>
+        <v>19330051920074</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
         <v>111</v>
@@ -4066,13 +3826,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920074</v>
+        <v>19330051920075</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
         <v>112</v>
@@ -4083,13 +3843,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920075</v>
+        <v>19330051920418</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D24" t="s">
         <v>113</v>
@@ -4105,7 +3865,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4137,16 +3897,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920045</v>
+        <v>18330051920078</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4155,21 +3915,21 @@
         <v>46</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920045</v>
+        <v>18330051920078</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4186,13 +3946,13 @@
         <v>19330051920081</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4209,13 +3969,13 @@
         <v>19330051920081</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4229,16 +3989,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920046</v>
+        <v>18330051920009</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -4252,39 +4012,39 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920055</v>
+        <v>19330051920045</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920056</v>
+        <v>19330051920046</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4298,16 +4058,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>18330051920022</v>
+        <v>19330051920055</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4321,16 +4081,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920074</v>
+        <v>19330051920056</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4339,6 +4099,98 @@
         <v>45</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>18330051920022</v>
+      </c>
+      <c r="B11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920059</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920068</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920074</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20211.xlsx
+++ b/grupos/5AEV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="114">
   <si>
     <t>Materia</t>
   </si>
@@ -164,12 +164,12 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>Bautista Sarao Eutiquio</t>
   </si>
   <si>
@@ -188,18 +188,57 @@
     <t>ARIZMENDI</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>COSCAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ESPINOSA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>DE JESUS</t>
   </si>
   <si>
+    <t>LARA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MEDRANO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
@@ -209,157 +248,118 @@
     <t>NUÑEZ</t>
   </si>
   <si>
-    <t>CHAVEZ</t>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>TZOPITL</t>
+  </si>
+  <si>
+    <t>VALIENTE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>VILLAR</t>
   </si>
   <si>
     <t>MONTERO</t>
   </si>
   <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>LOZANO</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CANSECO</t>
+  </si>
+  <si>
     <t>NOGALES</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>KARLA IRAN</t>
   </si>
   <si>
+    <t>CARLOS ADRIAN</t>
+  </si>
+  <si>
+    <t>EUSEBIO</t>
+  </si>
+  <si>
+    <t>ALMA LIZETH</t>
+  </si>
+  <si>
+    <t>LUIS ARIEL</t>
+  </si>
+  <si>
+    <t>YASIEL</t>
+  </si>
+  <si>
+    <t>GERARDO RAUL</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>MARTIN</t>
+  </si>
+  <si>
+    <t>ISAAC ALESSANDRO</t>
+  </si>
+  <si>
     <t>ALEXIS ARMANDO</t>
   </si>
   <si>
+    <t>AGUSTIN</t>
+  </si>
+  <si>
     <t>SALOMON</t>
   </si>
   <si>
+    <t>VICTOR SAUL</t>
+  </si>
+  <si>
     <t>ALEXIS YAIR</t>
   </si>
   <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JOSE DANIEL</t>
+  </si>
+  <si>
+    <t>IVAN</t>
+  </si>
+  <si>
     <t>JOSUE YAMIN</t>
   </si>
   <si>
-    <t>AGUSTIN</t>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>MARTI NEFTALI</t>
   </si>
   <si>
     <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>COSCAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ESPINOSA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>MEDRANO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>TZOPITL</t>
-  </si>
-  <si>
-    <t>VALIENTE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>VILLAR</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>LOZANO</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>CANSECO</t>
-  </si>
-  <si>
-    <t>CARLOS ADRIAN</t>
-  </si>
-  <si>
-    <t>EUSEBIO</t>
-  </si>
-  <si>
-    <t>ALMA LIZETH</t>
-  </si>
-  <si>
-    <t>LUIS ARIEL</t>
-  </si>
-  <si>
-    <t>YASIEL</t>
-  </si>
-  <si>
-    <t>GERARDO RAUL</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
-  </si>
-  <si>
-    <t>ISAAC ALESSANDRO</t>
-  </si>
-  <si>
-    <t>VICTOR SAUL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSE DANIEL</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>MARTI NEFTALI</t>
   </si>
 </sst>
 </file>
@@ -861,7 +861,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -882,67 +882,67 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>5</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>5</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>7</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X4">
         <v>5</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <v>5</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB4">
         <v>8</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -974,19 +974,19 @@
         <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z5">
         <v>5</v>
@@ -995,7 +995,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1042,49 +1042,49 @@
         <v>5</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>7</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>6</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1134,46 +1134,46 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB7">
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1223,46 +1223,46 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>10</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1273,16 +1273,16 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>5</v>
       </c>
       <c r="F9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -1294,64 +1294,64 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>7</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>5</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1401,25 +1401,25 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1431,7 +1431,7 @@
         <v>10</v>
       </c>
       <c r="Z10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>8</v>
@@ -1490,25 +1490,25 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1520,7 +1520,7 @@
         <v>9</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA11">
         <v>9</v>
@@ -1529,7 +1529,7 @@
         <v>9</v>
       </c>
       <c r="AC11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1579,25 +1579,25 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1606,19 +1606,19 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>8</v>
       </c>
       <c r="AC12">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1668,46 +1668,46 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>9</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z13">
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>10</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1736,7 +1736,7 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -1757,34 +1757,34 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>5</v>
@@ -1796,7 +1796,7 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1804,7 +1804,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1825,7 +1825,7 @@
         <v>5</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1837,55 +1837,55 @@
         <v>5</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>5</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>8</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1935,25 +1935,25 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -1962,10 +1962,10 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA16">
         <v>10</v>
@@ -2024,25 +2024,25 @@
         <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2054,16 +2054,16 @@
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2071,13 +2071,13 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -2092,55 +2092,55 @@
         <v>5</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>5</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z18">
         <v>5</v>
@@ -2149,10 +2149,10 @@
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2199,28 +2199,28 @@
         <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2229,10 +2229,10 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>6</v>
@@ -2241,7 +2241,7 @@
         <v>10</v>
       </c>
       <c r="AC19">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2291,31 +2291,31 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>7</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2359,10 +2359,10 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>9</v>
@@ -2377,43 +2377,43 @@
         <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>10</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>10</v>
@@ -2430,7 +2430,7 @@
         <v>7</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>7</v>
@@ -2448,55 +2448,55 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <v>5</v>
@@ -2508,7 +2508,7 @@
         <v>6</v>
       </c>
       <c r="AC22">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2558,25 +2558,25 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2588,7 +2588,7 @@
         <v>10</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA23">
         <v>10</v>
@@ -2597,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2644,31 +2644,31 @@
         <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2683,10 +2683,10 @@
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2694,19 +2694,19 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>5</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>5</v>
       </c>
       <c r="F25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G25">
         <v>6</v>
@@ -2715,64 +2715,64 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X25">
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z25">
         <v>5</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC25">
         <v>5</v>
@@ -2783,7 +2783,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -2804,10 +2804,10 @@
         <v>6</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>9</v>
@@ -2816,55 +2816,55 @@
         <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z26">
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB26">
         <v>6</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2929,16 +2929,16 @@
         <v>23</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F2">
-        <v>30.43</v>
+        <v>47.83</v>
       </c>
       <c r="G2">
-        <v>69.56999999999999</v>
+        <v>52.17</v>
       </c>
       <c r="H2">
         <v>5.6</v>
@@ -2961,25 +2961,25 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>68.18000000000001</v>
+        <v>77.27</v>
       </c>
       <c r="G3">
-        <v>18.18</v>
+        <v>22.73</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>13.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -2993,51 +2993,51 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>77.27</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>48</v>
       </c>
       <c r="C5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>81.81999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="G5">
-        <v>18.18</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3048,28 +3048,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>49</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>82.61</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>17.39</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3089,25 +3089,25 @@
         <v>23</v>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>86.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>13.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3121,25 +3121,25 @@
         <v>23</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3149,7 +3149,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3174,266 +3174,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920042</v>
-      </c>
-      <c r="B2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920058</v>
-      </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920050</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920050</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920050</v>
-      </c>
-      <c r="B6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920067</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920067</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>19330051920067</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>18330051920078</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>19330051920076</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>19330051920076</v>
-      </c>
-      <c r="B12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>19330051920076</v>
-      </c>
-      <c r="B13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" t="s">
-        <v>73</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>19330051920081</v>
-      </c>
-      <c r="B14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" t="s">
-        <v>74</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3469,132 +3209,132 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920050</v>
+        <v>19330051920042</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920067</v>
+        <v>18330051920009</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920076</v>
+        <v>19330051920045</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920042</v>
+        <v>19330051920046</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920058</v>
+        <v>19330051920049</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>18330051920078</v>
+        <v>19330051920053</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920081</v>
+        <v>19330051920055</v>
       </c>
       <c r="B8" t="s">
         <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>18330051920009</v>
+        <v>19330051920057</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
         <v>99</v>
@@ -3605,13 +3345,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920045</v>
+        <v>19330051920056</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
         <v>100</v>
@@ -3622,13 +3362,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920046</v>
+        <v>18330051920022</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
         <v>101</v>
@@ -3639,13 +3379,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920049</v>
+        <v>19330051920058</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
         <v>102</v>
@@ -3656,13 +3396,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>19330051920053</v>
+        <v>19330051920059</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="D13" t="s">
         <v>103</v>
@@ -3673,13 +3413,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>19330051920055</v>
+        <v>19330051920050</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>104</v>
@@ -3690,13 +3430,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920057</v>
+        <v>19330051920064</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D15" t="s">
         <v>105</v>
@@ -3707,13 +3447,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920056</v>
+        <v>19330051920067</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
         <v>106</v>
@@ -3724,13 +3464,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>18330051920022</v>
+        <v>19330051920068</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="D17" t="s">
         <v>107</v>
@@ -3741,16 +3481,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920059</v>
+        <v>19330051920069</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -3758,16 +3498,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920064</v>
+        <v>19330051920074</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -3775,16 +3515,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920068</v>
+        <v>18330051920078</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -3792,16 +3532,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>19330051920069</v>
+        <v>19330051920075</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -3809,16 +3549,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920074</v>
+        <v>19330051920418</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -3826,16 +3566,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920075</v>
+        <v>19330051920076</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -3843,13 +3583,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920418</v>
+        <v>19330051920081</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
         <v>113</v>
@@ -3865,7 +3605,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3897,39 +3637,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>18330051920078</v>
+        <v>19330051920067</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>18330051920078</v>
+        <v>19330051920067</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -3943,39 +3683,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920081</v>
+        <v>19330051920418</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920081</v>
+        <v>19330051920418</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -3989,22 +3729,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920009</v>
+        <v>19330051920081</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4012,22 +3752,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920045</v>
+        <v>19330051920081</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4035,16 +3775,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920046</v>
+        <v>18330051920009</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -4058,16 +3798,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920055</v>
+        <v>19330051920045</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4081,16 +3821,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920056</v>
+        <v>19330051920049</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4107,13 +3847,13 @@
         <v>18330051920022</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -4127,16 +3867,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920059</v>
+        <v>19330051920058</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4150,16 +3890,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920068</v>
+        <v>19330051920050</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -4168,29 +3908,6 @@
         <v>45</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920074</v>
-      </c>
-      <c r="B14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14">
         <v>5</v>
       </c>
     </row>
